--- a/Result/profitability/1340.xlsx
+++ b/Result/profitability/1340.xlsx
@@ -7291,21 +7291,21 @@
         <v>-100</v>
       </c>
       <c r="D55" t="n">
-        <v>-116</v>
+        <v>-98</v>
       </c>
       <c r="E55" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
         <v>-40</v>
@@ -7406,27 +7406,27 @@
         <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E56" t="n">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="F56" t="n">
-        <v>-118.96</v>
+        <v>-187.09</v>
       </c>
       <c r="G56" t="n">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-391.42%</t>
+          <t>-400.96%</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>-213</v>
       </c>
       <c r="J56" t="n">
-        <v>-251</v>
+        <v>-252</v>
       </c>
       <c r="K56" t="n">
         <v>-253</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.9088575096277278</v>
+        <v>2.002086007702182</v>
       </c>
       <c r="AA56" t="n">
         <v>1.31</v>
@@ -7479,10 +7479,10 @@
         <v>-0.4410774410774412</v>
       </c>
       <c r="AC56" t="n">
-        <v>-96.69</v>
+        <v>-164.82</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.34171531207903</v>
+        <v>7.400987876066457</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7592,10 +7592,10 @@
         <v>-0.8192771084337349</v>
       </c>
       <c r="Y57" t="n">
-        <v>-62.31000000000002</v>
+        <v>5.819999999999993</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.5237895090786822</v>
+        <v>-0.03110802287669034</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.02999999999999997</v>
@@ -7616,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH57" t="n">
         <v>0</v>
